--- a/google play/reports/eda_section_d_workbook.xlsx
+++ b/google play/reports/eda_section_d_workbook.xlsx
@@ -435,11 +435,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>game</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1581</v>
+        <v>9144</v>
       </c>
     </row>
     <row r="3">
@@ -448,11 +448,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>985</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="4">
@@ -461,11 +461,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>love</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>879</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="5">
@@ -474,11 +474,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>play</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>821</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6">
@@ -487,11 +487,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>playing</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>815</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="7">
@@ -500,11 +500,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>800</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="8">
@@ -513,11 +513,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>790</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="9">
@@ -526,11 +526,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>676</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="10">
@@ -539,11 +539,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>great</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>656</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11">
@@ -552,11 +552,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>levels</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>632</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="12">
@@ -565,11 +565,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>628</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="13">
@@ -578,11 +578,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>now</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>609</v>
+        <v>897</v>
       </c>
     </row>
     <row r="14">
@@ -591,11 +591,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>please</t>
+          <t>games</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>603</v>
+        <v>744</v>
       </c>
     </row>
     <row r="15">
@@ -604,11 +604,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ve</t>
+          <t>money</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>506</v>
+        <v>701</v>
       </c>
     </row>
     <row r="16">
@@ -617,11 +617,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>want</t>
+          <t>ve</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>499</v>
+        <v>652</v>
       </c>
     </row>
     <row r="17">
@@ -630,11 +630,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>494</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18">
@@ -643,11 +643,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>many</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>452</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19">
@@ -656,11 +656,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>update</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>441</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20">
@@ -669,11 +669,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>coins</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>433</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21">
@@ -682,11 +682,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>many</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22">
@@ -695,11 +695,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23">
@@ -708,11 +708,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>reader</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>380</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24">
@@ -721,11 +721,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>moves</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>371</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25">
@@ -734,11 +734,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>played</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>371</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26">
@@ -747,11 +747,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>364</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>359</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28">
@@ -773,11 +773,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>need</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29">
@@ -786,11 +786,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>enjoy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>any</t>
+          <t>best</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31">
@@ -812,11 +812,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>without</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,11 +856,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>507</v>
+        <v>295</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
@@ -870,13 +870,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ads</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>667</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>addictive</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -884,13 +884,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>413</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>757</v>
+      </c>
+      <c r="D4" t="n">
+        <v>252</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -898,13 +900,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>729</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>am</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>184</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -912,12 +914,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>amazing</t>
+          <t>awesome</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
@@ -926,13 +928,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bad</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>255</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>317</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -940,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>challenging</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>674</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
@@ -954,13 +956,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
-        <v>122</v>
-      </c>
+          <t>coins</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>287</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -968,12 +970,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>books</t>
+          <t>enjoy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -982,13 +984,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>289</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>373</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1459</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -996,12 +1000,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2959</v>
+      </c>
       <c r="D12" t="n">
-        <v>294</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="13">
@@ -1010,12 +1016,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>features</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>261</v>
+      </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14">
@@ -1024,13 +1032,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fix</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>238</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>563</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1038,12 +1046,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>great</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>150</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16">
@@ -1052,14 +1060,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>297</v>
+        <v>627</v>
       </c>
       <c r="D16" t="n">
-        <v>902</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -1068,12 +1076,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>great</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>levels</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>540</v>
+      </c>
       <c r="D17" t="n">
-        <v>511</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
@@ -1082,12 +1092,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>learn</t>
+          <t>love</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>161</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="19">
@@ -1096,13 +1106,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>learning</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>157</v>
-      </c>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>217</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1110,13 +1120,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>love</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
-        <v>577</v>
-      </c>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>458</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1124,15 +1134,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>many</t>
+          <t>moves</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>249</v>
-      </c>
-      <c r="D21" t="n">
-        <v>119</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1140,13 +1148,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>206</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>179</v>
+      </c>
+      <c r="D22" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1154,14 +1164,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>383</v>
-      </c>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>144</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
@@ -1170,13 +1178,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>248</v>
-      </c>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>238</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1188,10 +1196,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>715</v>
+        <v>485</v>
       </c>
       <c r="D25" t="n">
-        <v>150</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26">
@@ -1204,7 +1212,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
@@ -1214,13 +1222,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>play</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>764</v>
+      </c>
+      <c r="D27" t="n">
+        <v>910</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1228,14 +1238,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>please</t>
+          <t>playing</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>294</v>
+        <v>431</v>
       </c>
       <c r="D28" t="n">
-        <v>161</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29">
@@ -1244,14 +1254,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>204</v>
-      </c>
+          <t>relaxing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>170</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30">
@@ -1260,13 +1268,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>reader</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
-        <v>228</v>
-      </c>
+          <t>spend</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>199</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1274,14 +1282,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reading</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>274</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>253</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32">
@@ -1290,12 +1296,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>thank</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>480</v>
+      </c>
       <c r="D32" t="n">
-        <v>151</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33">
@@ -1304,15 +1312,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>update</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>383</v>
-      </c>
-      <c r="D33" t="n">
-        <v>151</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1320,13 +1326,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>tv</t>
+          <t>ve</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>228</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>274</v>
+      </c>
+      <c r="D34" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1334,11 +1342,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>want</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>480</v>
+        <v>173</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
@@ -1348,15 +1356,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ve</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>179</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1364,11 +1370,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>without</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>349</v>
+        <v>212</v>
       </c>
       <c r="D37" t="inlineStr"/>
     </row>
@@ -1378,56 +1384,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>206</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>want</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>291</v>
-      </c>
-      <c r="D39" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>272</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="n">
-        <v>156</v>
+        <v>185</v>
+      </c>
+      <c r="D38" t="n">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
